--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104547_W10.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104547_W10.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>J. PRADILLA</t>
+          <t>J. MONTERO</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,64 +565,64 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>6.8183</v>
+        <v>7.3053</v>
       </c>
       <c r="E2" t="n">
-        <v>4.4235</v>
+        <v>4.9832</v>
       </c>
       <c r="F2" t="n">
-        <v>2.3948</v>
+        <v>2.322</v>
       </c>
       <c r="G2" t="n">
-        <v>1.3961</v>
+        <v>2.604</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.0965</v>
+        <v>-1.5704</v>
       </c>
       <c r="I2" t="n">
-        <v>1.4927</v>
+        <v>4.1745</v>
       </c>
       <c r="J2" t="n">
-        <v>2.0696</v>
+        <v>2.6759</v>
       </c>
       <c r="K2" t="n">
-        <v>0.9902</v>
+        <v>-0.6075</v>
       </c>
       <c r="L2" t="n">
-        <v>1.0795</v>
+        <v>3.2834</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.6735</v>
+        <v>-0.07190000000000001</v>
       </c>
       <c r="N2" t="n">
-        <v>-1.0867</v>
+        <v>-0.9629</v>
       </c>
       <c r="O2" t="n">
-        <v>0.4132</v>
+        <v>0.8911</v>
       </c>
       <c r="P2" t="n">
-        <v>1.1342</v>
+        <v>2.0487</v>
       </c>
       <c r="Q2" t="n">
-        <v>-1.1342</v>
+        <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>2.2683</v>
+        <v>2.0487</v>
       </c>
       <c r="S2" t="n">
-        <v>3.1953</v>
+        <v>1.0184</v>
       </c>
       <c r="T2" t="n">
-        <v>2.3954</v>
+        <v>0.6731</v>
       </c>
       <c r="U2" t="n">
-        <v>0.8</v>
+        <v>0.3452</v>
       </c>
       <c r="V2" t="n">
-        <v>1.0927</v>
+        <v>1.6342</v>
       </c>
       <c r="W2" t="n">
-        <v>1.0927</v>
+        <v>1.6342</v>
       </c>
       <c r="X2" t="n">
         <v>0</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>S. DE LARREA</t>
+          <t>B. BADIO</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,64 +643,64 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>6.7688</v>
+        <v>6.3393</v>
       </c>
       <c r="E3" t="n">
-        <v>4.2754</v>
+        <v>3.9175</v>
       </c>
       <c r="F3" t="n">
-        <v>2.4935</v>
+        <v>2.4217</v>
       </c>
       <c r="G3" t="n">
-        <v>2.0933</v>
+        <v>0.669</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.2657</v>
+        <v>-0.4803</v>
       </c>
       <c r="I3" t="n">
-        <v>2.359</v>
+        <v>1.1493</v>
       </c>
       <c r="J3" t="n">
-        <v>2.8489</v>
+        <v>0.5541</v>
       </c>
       <c r="K3" t="n">
-        <v>0.7272999999999999</v>
+        <v>0.1379</v>
       </c>
       <c r="L3" t="n">
-        <v>2.1216</v>
+        <v>0.4162</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.7557</v>
+        <v>0.1149</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.993</v>
+        <v>-0.6182</v>
       </c>
       <c r="O3" t="n">
-        <v>0.2373</v>
+        <v>0.7331</v>
       </c>
       <c r="P3" t="n">
-        <v>-1.361</v>
+        <v>2.2763</v>
       </c>
       <c r="Q3" t="n">
-        <v>-4.5367</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>3.1757</v>
+        <v>2.2763</v>
       </c>
       <c r="S3" t="n">
-        <v>2.0515</v>
+        <v>0.1255</v>
       </c>
       <c r="T3" t="n">
-        <v>1.978</v>
+        <v>0.095</v>
       </c>
       <c r="U3" t="n">
-        <v>0.0735</v>
+        <v>0.0305</v>
       </c>
       <c r="V3" t="n">
-        <v>3.9851</v>
+        <v>3.2684</v>
       </c>
       <c r="W3" t="n">
-        <v>3.9851</v>
+        <v>3.2684</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>B. BADIO</t>
+          <t>S. DE LARREA</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,64 +721,64 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>5.9278</v>
+        <v>6.2755</v>
       </c>
       <c r="E4" t="n">
-        <v>3.5934</v>
+        <v>3.5265</v>
       </c>
       <c r="F4" t="n">
-        <v>2.3344</v>
+        <v>2.7491</v>
       </c>
       <c r="G4" t="n">
-        <v>0.6725</v>
+        <v>2.1015</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.4922</v>
+        <v>-0.2534</v>
       </c>
       <c r="I4" t="n">
-        <v>1.1647</v>
+        <v>2.3549</v>
       </c>
       <c r="J4" t="n">
-        <v>0.5755</v>
+        <v>2.8311</v>
       </c>
       <c r="K4" t="n">
-        <v>0.1385</v>
+        <v>0.7239</v>
       </c>
       <c r="L4" t="n">
-        <v>0.437</v>
+        <v>2.1072</v>
       </c>
       <c r="M4" t="n">
-        <v>0.097</v>
+        <v>-0.7296</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.6308</v>
+        <v>-0.9774</v>
       </c>
       <c r="O4" t="n">
-        <v>0.7277</v>
+        <v>0.2477</v>
       </c>
       <c r="P4" t="n">
-        <v>2.2683</v>
+        <v>-1.3658</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>-4.5526</v>
       </c>
       <c r="R4" t="n">
-        <v>2.2683</v>
+        <v>3.1868</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.291</v>
+        <v>1.5689</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.2601</v>
+        <v>1.2771</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.0309</v>
+        <v>0.2919</v>
       </c>
       <c r="V4" t="n">
-        <v>3.278</v>
+        <v>3.9709</v>
       </c>
       <c r="W4" t="n">
-        <v>3.278</v>
+        <v>3.9709</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>J. MONTERO</t>
+          <t>J. PRADILLA</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,64 +799,64 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>5.8138</v>
+        <v>5.7145</v>
       </c>
       <c r="E5" t="n">
-        <v>3.5502</v>
+        <v>3.4537</v>
       </c>
       <c r="F5" t="n">
-        <v>2.2636</v>
+        <v>2.2608</v>
       </c>
       <c r="G5" t="n">
-        <v>2.6357</v>
+        <v>1.3837</v>
       </c>
       <c r="H5" t="n">
-        <v>-1.5597</v>
+        <v>-0.1058</v>
       </c>
       <c r="I5" t="n">
-        <v>4.1954</v>
+        <v>1.4895</v>
       </c>
       <c r="J5" t="n">
-        <v>2.7278</v>
+        <v>2.044</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.5826</v>
+        <v>0.9718</v>
       </c>
       <c r="L5" t="n">
-        <v>3.3104</v>
+        <v>1.0722</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.0921</v>
+        <v>-0.6603</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.9771</v>
+        <v>-1.0775</v>
       </c>
       <c r="O5" t="n">
-        <v>0.885</v>
+        <v>0.4173</v>
       </c>
       <c r="P5" t="n">
-        <v>2.0415</v>
+        <v>1.1382</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>-1.1382</v>
       </c>
       <c r="R5" t="n">
-        <v>2.0415</v>
+        <v>2.2763</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.5024</v>
+        <v>2.1032</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.8166</v>
+        <v>1.4584</v>
       </c>
       <c r="U5" t="n">
-        <v>0.3142</v>
+        <v>0.6448</v>
       </c>
       <c r="V5" t="n">
-        <v>1.639</v>
+        <v>1.0895</v>
       </c>
       <c r="W5" t="n">
-        <v>1.639</v>
+        <v>1.0895</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>X. LOPEZ-AROSTEGUI</t>
+          <t>O. MOORE</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>5.562</v>
+        <v>5.4052</v>
       </c>
       <c r="E6" t="n">
-        <v>3.2765</v>
+        <v>4.5072</v>
       </c>
       <c r="F6" t="n">
-        <v>2.2855</v>
+        <v>0.898</v>
       </c>
       <c r="G6" t="n">
-        <v>2.1564</v>
+        <v>3.2386</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.6984</v>
+        <v>2.2781</v>
       </c>
       <c r="I6" t="n">
-        <v>2.8548</v>
+        <v>0.9605</v>
       </c>
       <c r="J6" t="n">
-        <v>2.5899</v>
+        <v>3.6972</v>
       </c>
       <c r="K6" t="n">
-        <v>0.0897</v>
+        <v>3.5713</v>
       </c>
       <c r="L6" t="n">
-        <v>2.5002</v>
+        <v>0.1259</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.4335</v>
+        <v>-0.4587</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.788</v>
+        <v>-1.2932</v>
       </c>
       <c r="O6" t="n">
-        <v>0.3546</v>
+        <v>0.8345</v>
       </c>
       <c r="P6" t="n">
-        <v>1.1342</v>
+        <v>2.0487</v>
       </c>
       <c r="Q6" t="n">
-        <v>-1.1342</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>2.2683</v>
+        <v>2.0487</v>
       </c>
       <c r="S6" t="n">
-        <v>2.2714</v>
+        <v>1.0497</v>
       </c>
       <c r="T6" t="n">
-        <v>1.8207</v>
+        <v>0.6522</v>
       </c>
       <c r="U6" t="n">
-        <v>0.4506</v>
+        <v>0.3975</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>-0.9317</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>0.1578</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>O. MOORE</t>
+          <t>X. LOPEZ-AROSTEGUI</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,67 +955,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>4.6873</v>
+        <v>4.5078</v>
       </c>
       <c r="E7" t="n">
-        <v>3.8846</v>
+        <v>2.196</v>
       </c>
       <c r="F7" t="n">
-        <v>0.8028</v>
+        <v>2.3118</v>
       </c>
       <c r="G7" t="n">
-        <v>3.2548</v>
+        <v>2.155</v>
       </c>
       <c r="H7" t="n">
-        <v>2.2872</v>
+        <v>-0.7007</v>
       </c>
       <c r="I7" t="n">
-        <v>0.9675</v>
+        <v>2.8556</v>
       </c>
       <c r="J7" t="n">
-        <v>3.7359</v>
+        <v>2.5703</v>
       </c>
       <c r="K7" t="n">
-        <v>3.5948</v>
+        <v>0.0755</v>
       </c>
       <c r="L7" t="n">
-        <v>0.1411</v>
+        <v>2.4949</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.4812</v>
+        <v>-0.4154</v>
       </c>
       <c r="N7" t="n">
-        <v>-1.3075</v>
+        <v>-0.7761</v>
       </c>
       <c r="O7" t="n">
-        <v>0.8264</v>
+        <v>0.3608</v>
       </c>
       <c r="P7" t="n">
-        <v>2.0415</v>
+        <v>1.1382</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>-1.1382</v>
       </c>
       <c r="R7" t="n">
-        <v>2.0415</v>
+        <v>2.2763</v>
       </c>
       <c r="S7" t="n">
-        <v>0.323</v>
+        <v>1.2147</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.0121</v>
+        <v>0.7638</v>
       </c>
       <c r="U7" t="n">
-        <v>0.3351</v>
+        <v>0.4509</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.9320000000000001</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>0.1607</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-1.0927</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>4.0522</v>
+        <v>3.4944</v>
       </c>
       <c r="E8" t="n">
-        <v>1.9119</v>
+        <v>1.7663</v>
       </c>
       <c r="F8" t="n">
-        <v>2.1403</v>
+        <v>1.7282</v>
       </c>
       <c r="G8" t="n">
-        <v>3.185</v>
+        <v>3.1796</v>
       </c>
       <c r="H8" t="n">
-        <v>0.3089</v>
+        <v>0.3047</v>
       </c>
       <c r="I8" t="n">
-        <v>2.8761</v>
+        <v>2.8749</v>
       </c>
       <c r="J8" t="n">
-        <v>2.1126</v>
+        <v>2.0882</v>
       </c>
       <c r="K8" t="n">
-        <v>0.436</v>
+        <v>0.4202</v>
       </c>
       <c r="L8" t="n">
-        <v>1.6765</v>
+        <v>1.668</v>
       </c>
       <c r="M8" t="n">
-        <v>1.0724</v>
+        <v>1.0914</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.1272</v>
+        <v>-0.1155</v>
       </c>
       <c r="O8" t="n">
-        <v>1.1995</v>
+        <v>1.2069</v>
       </c>
       <c r="P8" t="n">
-        <v>0.4537</v>
+        <v>0.4553</v>
       </c>
       <c r="Q8" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R8" t="n">
-        <v>1.5878</v>
+        <v>1.5934</v>
       </c>
       <c r="S8" t="n">
-        <v>0.9599</v>
+        <v>0.4043</v>
       </c>
       <c r="T8" t="n">
-        <v>0.3871</v>
+        <v>0.2715</v>
       </c>
       <c r="U8" t="n">
-        <v>0.5728</v>
+        <v>0.1328</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.5463</v>
+        <v>-0.5447</v>
       </c>
       <c r="W8" t="n">
-        <v>0.5463</v>
+        <v>0.5447</v>
       </c>
       <c r="X8" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="9">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>2.1742</v>
+        <v>2.5235</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.7202</v>
+        <v>-0.09420000000000001</v>
       </c>
       <c r="F9" t="n">
-        <v>2.8944</v>
+        <v>2.6177</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.0396</v>
+        <v>-0.0455</v>
       </c>
       <c r="H9" t="n">
-        <v>0.1471</v>
+        <v>0.1547</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.1867</v>
+        <v>-0.2002</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.6484</v>
+        <v>-0.6792</v>
       </c>
       <c r="K9" t="n">
-        <v>0.1487</v>
+        <v>0.1411</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.7972</v>
+        <v>-0.8203</v>
       </c>
       <c r="M9" t="n">
-        <v>0.6088</v>
+        <v>0.6336000000000001</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.0017</v>
+        <v>0.0135</v>
       </c>
       <c r="O9" t="n">
-        <v>0.6105</v>
+        <v>0.6201</v>
       </c>
       <c r="P9" t="n">
-        <v>1.5878</v>
+        <v>1.5934</v>
       </c>
       <c r="Q9" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R9" t="n">
-        <v>2.722</v>
+        <v>2.7316</v>
       </c>
       <c r="S9" t="n">
-        <v>0.6261</v>
+        <v>0.9756</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.0302</v>
+        <v>0.6337</v>
       </c>
       <c r="U9" t="n">
-        <v>0.6563</v>
+        <v>0.3419</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="X9" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="10">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>0.4978</v>
+        <v>0.6796</v>
       </c>
       <c r="E10" t="n">
-        <v>0.7000999999999999</v>
+        <v>0.8105</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.2022</v>
+        <v>-0.1309</v>
       </c>
       <c r="G10" t="n">
-        <v>0.4611</v>
+        <v>0.4578</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.5252</v>
+        <v>-0.5283</v>
       </c>
       <c r="I10" t="n">
-        <v>0.9862</v>
+        <v>0.9861</v>
       </c>
       <c r="J10" t="n">
-        <v>0.6819</v>
+        <v>0.6735</v>
       </c>
       <c r="K10" t="n">
-        <v>0.0102</v>
+        <v>0.0033</v>
       </c>
       <c r="L10" t="n">
-        <v>0.6717</v>
+        <v>0.6703</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.2209</v>
+        <v>-0.2157</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.5354</v>
+        <v>-0.5315</v>
       </c>
       <c r="O10" t="n">
-        <v>0.3145</v>
+        <v>0.3159</v>
       </c>
       <c r="P10" t="n">
-        <v>0.4537</v>
+        <v>0.4553</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>0.4537</v>
+        <v>0.4553</v>
       </c>
       <c r="S10" t="n">
-        <v>0.1294</v>
+        <v>0.3112</v>
       </c>
       <c r="T10" t="n">
-        <v>0.0181</v>
+        <v>0.137</v>
       </c>
       <c r="U10" t="n">
-        <v>0.1113</v>
+        <v>0.1743</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.5463</v>
+        <v>-0.5447</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.5463</v>
+        <v>-0.5447</v>
       </c>
     </row>
     <row r="11">
@@ -1267,73 +1267,73 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>0.1446</v>
+        <v>0.577</v>
       </c>
       <c r="E11" t="n">
-        <v>0.273</v>
+        <v>0.4933</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.1284</v>
+        <v>0.0837</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.3695</v>
+        <v>-0.3753</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.6175</v>
+        <v>-0.6257</v>
       </c>
       <c r="I11" t="n">
-        <v>0.2479</v>
+        <v>0.2504</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.1837</v>
+        <v>-0.2033</v>
       </c>
       <c r="K11" t="n">
-        <v>0.4533</v>
+        <v>0.4374</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.6371</v>
+        <v>-0.6407</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.1858</v>
+        <v>-0.172</v>
       </c>
       <c r="N11" t="n">
-        <v>-1.0708</v>
+        <v>-1.0631</v>
       </c>
       <c r="O11" t="n">
-        <v>0.885</v>
+        <v>0.8911</v>
       </c>
       <c r="P11" t="n">
-        <v>1.361</v>
+        <v>1.3658</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>1.361</v>
+        <v>1.3658</v>
       </c>
       <c r="S11" t="n">
-        <v>0.4065</v>
+        <v>0.8338</v>
       </c>
       <c r="T11" t="n">
-        <v>0.4567</v>
+        <v>0.6965</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.0502</v>
+        <v>0.1372</v>
       </c>
       <c r="V11" t="n">
-        <v>-1.2534</v>
+        <v>-1.2472</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>-1.2534</v>
+        <v>-1.2472</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>B. KEY</t>
+          <t>N. SAKO</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,73 +1345,73 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.057</v>
+        <v>0.1291</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.0648</v>
+        <v>-0.4644</v>
       </c>
       <c r="F12" t="n">
-        <v>0.0077</v>
+        <v>0.5935</v>
       </c>
       <c r="G12" t="n">
-        <v>-1.5776</v>
+        <v>-2.07</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.6047</v>
+        <v>-2.6824</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.9729</v>
+        <v>0.6124000000000001</v>
       </c>
       <c r="J12" t="n">
-        <v>-1.0296</v>
+        <v>-0.6217</v>
       </c>
       <c r="K12" t="n">
-        <v>0.3565</v>
+        <v>-1.4037</v>
       </c>
       <c r="L12" t="n">
-        <v>-1.3861</v>
+        <v>0.782</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.548</v>
+        <v>-1.4483</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.9612000000000001</v>
+        <v>-1.2788</v>
       </c>
       <c r="O12" t="n">
-        <v>0.4132</v>
+        <v>-0.1695</v>
       </c>
       <c r="P12" t="n">
-        <v>0.9073</v>
+        <v>1.5934</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>-1.1382</v>
       </c>
       <c r="R12" t="n">
-        <v>0.9073</v>
+        <v>2.7316</v>
       </c>
       <c r="S12" t="n">
-        <v>0.774</v>
+        <v>1.5374</v>
       </c>
       <c r="T12" t="n">
-        <v>0.9648</v>
+        <v>1.1377</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.1909</v>
+        <v>0.3997</v>
       </c>
       <c r="V12" t="n">
-        <v>-0.1607</v>
+        <v>-0.9317</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>0.1578</v>
       </c>
       <c r="X12" t="n">
-        <v>-0.1607</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>N. SAKO</t>
+          <t>B. KEY</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,67 +1423,67 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-0.4428</v>
+        <v>-0.6553</v>
       </c>
       <c r="E13" t="n">
-        <v>-0.7534</v>
+        <v>-0.7156</v>
       </c>
       <c r="F13" t="n">
-        <v>0.3106</v>
+        <v>0.0603</v>
       </c>
       <c r="G13" t="n">
-        <v>-2.0732</v>
+        <v>-1.5763</v>
       </c>
       <c r="H13" t="n">
-        <v>-2.681</v>
+        <v>-0.6005</v>
       </c>
       <c r="I13" t="n">
-        <v>0.6078</v>
+        <v>-0.9758</v>
       </c>
       <c r="J13" t="n">
-        <v>-0.6057</v>
+        <v>-1.0451</v>
       </c>
       <c r="K13" t="n">
-        <v>-1.3893</v>
+        <v>0.348</v>
       </c>
       <c r="L13" t="n">
-        <v>0.7837</v>
+        <v>-1.3931</v>
       </c>
       <c r="M13" t="n">
-        <v>-1.4675</v>
+        <v>-0.5312</v>
       </c>
       <c r="N13" t="n">
-        <v>-1.2917</v>
+        <v>-0.9485</v>
       </c>
       <c r="O13" t="n">
-        <v>-0.1759</v>
+        <v>0.4173</v>
       </c>
       <c r="P13" t="n">
-        <v>1.5878</v>
+        <v>0.9105</v>
       </c>
       <c r="Q13" t="n">
-        <v>-1.1342</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>2.722</v>
+        <v>0.9105</v>
       </c>
       <c r="S13" t="n">
-        <v>0.9745</v>
+        <v>0.1683</v>
       </c>
       <c r="T13" t="n">
-        <v>0.8257</v>
+        <v>0.3295</v>
       </c>
       <c r="U13" t="n">
-        <v>0.1488</v>
+        <v>-0.1612</v>
       </c>
       <c r="V13" t="n">
-        <v>-0.9320000000000001</v>
+        <v>-0.1578</v>
       </c>
       <c r="W13" t="n">
-        <v>0.1607</v>
+        <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>-1.0927</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="14">
@@ -1501,67 +1501,67 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>41.947</v>
+        <v>42.2959</v>
       </c>
       <c r="E14" t="n">
-        <v>24.35019999999999</v>
+        <v>24.38</v>
       </c>
       <c r="F14" t="n">
-        <v>17.597</v>
+        <v>17.9159</v>
       </c>
       <c r="G14" t="n">
-        <v>11.795</v>
+        <v>11.7221</v>
       </c>
       <c r="H14" t="n">
-        <v>-4.797700000000001</v>
+        <v>-4.81</v>
       </c>
       <c r="I14" t="n">
-        <v>16.5925</v>
+        <v>16.5321</v>
       </c>
       <c r="J14" t="n">
-        <v>14.8747</v>
+        <v>14.585</v>
       </c>
       <c r="K14" t="n">
-        <v>4.9733</v>
+        <v>4.8192</v>
       </c>
       <c r="L14" t="n">
-        <v>9.901299999999997</v>
+        <v>9.765999999999998</v>
       </c>
       <c r="M14" t="n">
-        <v>-3.08</v>
+        <v>-2.8632</v>
       </c>
       <c r="N14" t="n">
-        <v>-9.771100000000001</v>
+        <v>-9.629199999999999</v>
       </c>
       <c r="O14" t="n">
-        <v>6.691</v>
+        <v>6.7663</v>
       </c>
       <c r="P14" t="n">
-        <v>13.61</v>
+        <v>13.658</v>
       </c>
       <c r="Q14" t="n">
-        <v>-10.2077</v>
+        <v>-10.2436</v>
       </c>
       <c r="R14" t="n">
-        <v>23.8174</v>
+        <v>23.9013</v>
       </c>
       <c r="S14" t="n">
-        <v>10.9182</v>
+        <v>11.311</v>
       </c>
       <c r="T14" t="n">
-        <v>7.7275</v>
+        <v>8.125500000000001</v>
       </c>
       <c r="U14" t="n">
-        <v>3.1906</v>
+        <v>3.185500000000001</v>
       </c>
       <c r="V14" t="n">
-        <v>5.624099999999999</v>
+        <v>5.605200000000001</v>
       </c>
       <c r="W14" t="n">
-        <v>11.9552</v>
+        <v>11.9128</v>
       </c>
       <c r="X14" t="n">
-        <v>-6.3312</v>
+        <v>-6.3077</v>
       </c>
     </row>
     <row r="15">
@@ -1579,64 +1579,64 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.193</v>
+        <v>1.7581</v>
       </c>
       <c r="E15" t="n">
-        <v>2.5627</v>
+        <v>2.7502</v>
       </c>
       <c r="F15" t="n">
-        <v>-1.3697</v>
+        <v>-0.9921</v>
       </c>
       <c r="G15" t="n">
-        <v>1.6224</v>
+        <v>1.6082</v>
       </c>
       <c r="H15" t="n">
-        <v>2.7738</v>
+        <v>2.7472</v>
       </c>
       <c r="I15" t="n">
-        <v>-1.1514</v>
+        <v>-1.139</v>
       </c>
       <c r="J15" t="n">
-        <v>3.7403</v>
+        <v>3.697</v>
       </c>
       <c r="K15" t="n">
-        <v>3.1059</v>
+        <v>3.0639</v>
       </c>
       <c r="L15" t="n">
-        <v>0.6344</v>
+        <v>0.633</v>
       </c>
       <c r="M15" t="n">
-        <v>-2.1179</v>
+        <v>-2.0888</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.3321</v>
+        <v>-0.3168</v>
       </c>
       <c r="O15" t="n">
-        <v>-1.7858</v>
+        <v>-1.772</v>
       </c>
       <c r="P15" t="n">
-        <v>0.2268</v>
+        <v>0.2276</v>
       </c>
       <c r="Q15" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R15" t="n">
-        <v>1.361</v>
+        <v>1.3658</v>
       </c>
       <c r="S15" t="n">
-        <v>-1.2025</v>
+        <v>-0.6225000000000001</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.5898</v>
+        <v>-0.3534</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.6128</v>
+        <v>-0.2691</v>
       </c>
       <c r="V15" t="n">
-        <v>0.5463</v>
+        <v>0.5447</v>
       </c>
       <c r="W15" t="n">
-        <v>0.5463</v>
+        <v>0.5447</v>
       </c>
       <c r="X15" t="n">
         <v>0</v>
@@ -1657,22 +1657,22 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.2614</v>
+        <v>0.2501</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.2087</v>
+        <v>0.0278</v>
       </c>
       <c r="F16" t="n">
-        <v>0.47</v>
+        <v>0.2223</v>
       </c>
       <c r="G16" t="n">
-        <v>0.09859999999999999</v>
+        <v>0.1014</v>
       </c>
       <c r="H16" t="n">
-        <v>0.1573</v>
+        <v>0.1579</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.0586</v>
+        <v>-0.0565</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -1684,13 +1684,13 @@
         <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>0.09859999999999999</v>
+        <v>0.1014</v>
       </c>
       <c r="N16" t="n">
-        <v>0.1573</v>
+        <v>0.1579</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.0586</v>
+        <v>-0.0565</v>
       </c>
       <c r="P16" t="n">
         <v>0</v>
@@ -1702,13 +1702,13 @@
         <v>0</v>
       </c>
       <c r="S16" t="n">
-        <v>0.1627</v>
+        <v>0.1487</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.2087</v>
+        <v>0.0278</v>
       </c>
       <c r="U16" t="n">
-        <v>0.3714</v>
+        <v>0.1209</v>
       </c>
       <c r="V16" t="n">
         <v>0</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>J. SORIANO</t>
+          <t>C. ALIAS</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,64 +1735,64 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-1.5161</v>
+        <v>-1.5732</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.9524</v>
+        <v>-1.0837</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.5637</v>
+        <v>-0.4895</v>
       </c>
       <c r="G17" t="n">
-        <v>-1.2497</v>
+        <v>-0.3468</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.8153</v>
+        <v>-0.1696</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.4344</v>
+        <v>-0.1772</v>
       </c>
       <c r="J17" t="n">
-        <v>0.2682</v>
+        <v>0.0545</v>
       </c>
       <c r="K17" t="n">
-        <v>0.1936</v>
+        <v>0.0172</v>
       </c>
       <c r="L17" t="n">
-        <v>0.0746</v>
+        <v>0.0372</v>
       </c>
       <c r="M17" t="n">
-        <v>-1.5179</v>
+        <v>-0.4012</v>
       </c>
       <c r="N17" t="n">
-        <v>-1.0089</v>
+        <v>-0.1868</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.509</v>
+        <v>-0.2144</v>
       </c>
       <c r="P17" t="n">
-        <v>-1.1342</v>
+        <v>-0.9105</v>
       </c>
       <c r="Q17" t="n">
-        <v>-2.4952</v>
+        <v>-1.1382</v>
       </c>
       <c r="R17" t="n">
-        <v>1.361</v>
+        <v>0.2276</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.3856</v>
+        <v>-0.3159</v>
       </c>
       <c r="T17" t="n">
-        <v>0.0212</v>
+        <v>0</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.4068</v>
+        <v>-0.3159</v>
       </c>
       <c r="V17" t="n">
-        <v>1.2534</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>1.2534</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
         <v>0</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>C. ALIAS</t>
+          <t>J. SORIANO</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,64 +1813,64 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.5722</v>
+        <v>-2.1447</v>
       </c>
       <c r="E18" t="n">
-        <v>-1.0795</v>
+        <v>-1.4542</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.4927</v>
+        <v>-0.6905</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.3503</v>
+        <v>-1.2355</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.1717</v>
+        <v>-0.8129</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.1786</v>
+        <v>-0.4225</v>
       </c>
       <c r="J18" t="n">
-        <v>0.0546</v>
+        <v>0.2533</v>
       </c>
       <c r="K18" t="n">
-        <v>0.0173</v>
+        <v>0.1789</v>
       </c>
       <c r="L18" t="n">
-        <v>0.0373</v>
+        <v>0.0745</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.405</v>
+        <v>-1.4888</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.1891</v>
+        <v>-0.9918</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.2159</v>
+        <v>-0.497</v>
       </c>
       <c r="P18" t="n">
-        <v>-0.9073</v>
+        <v>-1.1382</v>
       </c>
       <c r="Q18" t="n">
-        <v>-1.1342</v>
+        <v>-2.5039</v>
       </c>
       <c r="R18" t="n">
-        <v>0.2268</v>
+        <v>1.3658</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.3145</v>
+        <v>-1.0184</v>
       </c>
       <c r="T18" t="n">
-        <v>0</v>
+        <v>-0.4509</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.3145</v>
+        <v>-0.5675</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>1.2472</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>1.2472</v>
       </c>
       <c r="X18" t="n">
         <v>0</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>M. GONZALEZ</t>
+          <t>D. STEPHENS</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-2.5831</v>
+        <v>-2.6053</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.911</v>
+        <v>-0.9401</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.672</v>
+        <v>-1.6652</v>
       </c>
       <c r="G19" t="n">
-        <v>-1.1781</v>
+        <v>-1.6402</v>
       </c>
       <c r="H19" t="n">
-        <v>-1.3408</v>
+        <v>-0.9224</v>
       </c>
       <c r="I19" t="n">
-        <v>0.1627</v>
+        <v>-0.7178</v>
       </c>
       <c r="J19" t="n">
-        <v>0.3743</v>
+        <v>-0.7539</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.6304999999999999</v>
+        <v>-0.6345</v>
       </c>
       <c r="L19" t="n">
-        <v>1.0048</v>
+        <v>-0.1194</v>
       </c>
       <c r="M19" t="n">
-        <v>-1.5524</v>
+        <v>-0.8863</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.7103</v>
+        <v>-0.2879</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.8421999999999999</v>
+        <v>-0.5984</v>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>0.4553</v>
       </c>
       <c r="Q19" t="n">
-        <v>-1.1342</v>
+        <v>-0.2276</v>
       </c>
       <c r="R19" t="n">
-        <v>1.1342</v>
+        <v>0.6829</v>
       </c>
       <c r="S19" t="n">
-        <v>-1.2443</v>
+        <v>-0.1732</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.1512</v>
+        <v>0.0414</v>
       </c>
       <c r="U19" t="n">
-        <v>-1.0931</v>
+        <v>-0.2146</v>
       </c>
       <c r="V19" t="n">
-        <v>-0.1607</v>
+        <v>-1.2472</v>
       </c>
       <c r="W19" t="n">
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-0.1607</v>
+        <v>-1.2472</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>D. STEPHENS</t>
+          <t>M. GONZALEZ</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-3.2849</v>
+        <v>-2.6681</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.9327</v>
+        <v>-1.161</v>
       </c>
       <c r="F20" t="n">
-        <v>-2.3522</v>
+        <v>-1.5071</v>
       </c>
       <c r="G20" t="n">
-        <v>-1.6532</v>
+        <v>-1.1516</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.9308</v>
+        <v>-1.3249</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.7223000000000001</v>
+        <v>0.1733</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.7452</v>
+        <v>0.3632</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.6304999999999999</v>
+        <v>-0.6345</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.1147</v>
+        <v>0.9977</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.908</v>
+        <v>-1.5148</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.3003</v>
+        <v>-0.6904</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.6077</v>
+        <v>-0.8245</v>
       </c>
       <c r="P20" t="n">
-        <v>0.4537</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>-0.2268</v>
+        <v>-1.1382</v>
       </c>
       <c r="R20" t="n">
-        <v>0.6805</v>
+        <v>1.1382</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.832</v>
+        <v>-1.3587</v>
       </c>
       <c r="T20" t="n">
-        <v>0.0393</v>
+        <v>-0.386</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.8713</v>
+        <v>-0.9727</v>
       </c>
       <c r="V20" t="n">
-        <v>-1.2534</v>
+        <v>-0.1578</v>
       </c>
       <c r="W20" t="n">
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-1.2534</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="21">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-4.2661</v>
+        <v>-4.0193</v>
       </c>
       <c r="E21" t="n">
-        <v>1.9527</v>
+        <v>1.9065</v>
       </c>
       <c r="F21" t="n">
-        <v>-6.2188</v>
+        <v>-5.9258</v>
       </c>
       <c r="G21" t="n">
-        <v>0.3767</v>
+        <v>0.382</v>
       </c>
       <c r="H21" t="n">
-        <v>2.0692</v>
+        <v>2.068</v>
       </c>
       <c r="I21" t="n">
-        <v>-1.6926</v>
+        <v>-1.686</v>
       </c>
       <c r="J21" t="n">
-        <v>2.7313</v>
+        <v>2.7009</v>
       </c>
       <c r="K21" t="n">
-        <v>3.1099</v>
+        <v>3.0887</v>
       </c>
       <c r="L21" t="n">
-        <v>-0.3786</v>
+        <v>-0.3877</v>
       </c>
       <c r="M21" t="n">
-        <v>-2.3547</v>
+        <v>-2.3189</v>
       </c>
       <c r="N21" t="n">
-        <v>-1.0407</v>
+        <v>-1.0207</v>
       </c>
       <c r="O21" t="n">
-        <v>-1.314</v>
+        <v>-1.2982</v>
       </c>
       <c r="P21" t="n">
-        <v>-1.361</v>
+        <v>-1.3658</v>
       </c>
       <c r="Q21" t="n">
-        <v>-2.2683</v>
+        <v>-2.2763</v>
       </c>
       <c r="R21" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="S21" t="n">
-        <v>-2.5747</v>
+        <v>-2.333</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.6956</v>
+        <v>-0.697</v>
       </c>
       <c r="U21" t="n">
-        <v>-1.8791</v>
+        <v>-1.6359</v>
       </c>
       <c r="V21" t="n">
-        <v>-0.7071</v>
+        <v>-0.7025</v>
       </c>
       <c r="W21" t="n">
-        <v>2.1853</v>
+        <v>2.1789</v>
       </c>
       <c r="X21" t="n">
-        <v>-2.8924</v>
+        <v>-2.8814</v>
       </c>
     </row>
     <row r="22">
@@ -2125,73 +2125,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-5.0507</v>
+        <v>-4.7996</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.3153</v>
+        <v>-2.4875</v>
       </c>
       <c r="F22" t="n">
-        <v>-2.7354</v>
+        <v>-2.3121</v>
       </c>
       <c r="G22" t="n">
-        <v>0.0564</v>
+        <v>0.055</v>
       </c>
       <c r="H22" t="n">
-        <v>3.3217</v>
+        <v>3.3202</v>
       </c>
       <c r="I22" t="n">
-        <v>-3.2653</v>
+        <v>-3.2652</v>
       </c>
       <c r="J22" t="n">
-        <v>1.1688</v>
+        <v>1.1249</v>
       </c>
       <c r="K22" t="n">
-        <v>3.9065</v>
+        <v>3.8815</v>
       </c>
       <c r="L22" t="n">
-        <v>-2.7377</v>
+        <v>-2.7566</v>
       </c>
       <c r="M22" t="n">
-        <v>-1.1124</v>
+        <v>-1.0699</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.5848</v>
+        <v>-0.5613</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.5276</v>
+        <v>-0.5086000000000001</v>
       </c>
       <c r="P22" t="n">
-        <v>-2.2683</v>
+        <v>-2.2763</v>
       </c>
       <c r="Q22" t="n">
-        <v>-3.4025</v>
+        <v>-3.4145</v>
       </c>
       <c r="R22" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.1998</v>
+        <v>-0.944</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.08160000000000001</v>
+        <v>-0.1979</v>
       </c>
       <c r="U22" t="n">
-        <v>-1.1182</v>
+        <v>-0.7461</v>
       </c>
       <c r="V22" t="n">
-        <v>-1.639</v>
+        <v>-1.6342</v>
       </c>
       <c r="W22" t="n">
         <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>-1.639</v>
+        <v>-1.6342</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>J. FERNANDEZ</t>
+          <t>M. SPISSU</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,73 +2203,73 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-5.3586</v>
+        <v>-5.1222</v>
       </c>
       <c r="E23" t="n">
-        <v>-1.0001</v>
+        <v>-4.0302</v>
       </c>
       <c r="F23" t="n">
-        <v>-4.3585</v>
+        <v>-1.0919</v>
       </c>
       <c r="G23" t="n">
-        <v>-3.0247</v>
+        <v>-1.9561</v>
       </c>
       <c r="H23" t="n">
-        <v>-1.0203</v>
+        <v>0.8469</v>
       </c>
       <c r="I23" t="n">
-        <v>-2.0044</v>
+        <v>-2.8031</v>
       </c>
       <c r="J23" t="n">
-        <v>-1.3276</v>
+        <v>-0.3295</v>
       </c>
       <c r="K23" t="n">
-        <v>-0.5786</v>
+        <v>0.8479</v>
       </c>
       <c r="L23" t="n">
-        <v>-0.749</v>
+        <v>-1.1773</v>
       </c>
       <c r="M23" t="n">
-        <v>-1.6971</v>
+        <v>-1.6266</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.4417</v>
+        <v>-0.0009</v>
       </c>
       <c r="O23" t="n">
-        <v>-1.2554</v>
+        <v>-1.6257</v>
       </c>
       <c r="P23" t="n">
-        <v>0.2268</v>
+        <v>-2.2763</v>
       </c>
       <c r="Q23" t="n">
-        <v>-0.2268</v>
+        <v>-3.6421</v>
       </c>
       <c r="R23" t="n">
-        <v>0.4537</v>
+        <v>1.3658</v>
       </c>
       <c r="S23" t="n">
-        <v>0.1709</v>
+        <v>-1.0475</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.5383</v>
+        <v>-0.2164</v>
       </c>
       <c r="U23" t="n">
-        <v>0.7092000000000001</v>
+        <v>-0.8310999999999999</v>
       </c>
       <c r="V23" t="n">
-        <v>-2.7317</v>
+        <v>0.1578</v>
       </c>
       <c r="W23" t="n">
-        <v>1.0927</v>
+        <v>0.1578</v>
       </c>
       <c r="X23" t="n">
-        <v>-3.8243</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>M. SPISSU</t>
+          <t>J. FERNANDEZ</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,67 +2281,67 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-5.8194</v>
+        <v>-5.4102</v>
       </c>
       <c r="E24" t="n">
-        <v>-3.8746</v>
+        <v>-0.7756</v>
       </c>
       <c r="F24" t="n">
-        <v>-1.9448</v>
+        <v>-4.6346</v>
       </c>
       <c r="G24" t="n">
-        <v>-1.9709</v>
+        <v>-3.0083</v>
       </c>
       <c r="H24" t="n">
-        <v>0.8411</v>
+        <v>-1.0142</v>
       </c>
       <c r="I24" t="n">
-        <v>-2.8121</v>
+        <v>-1.9941</v>
       </c>
       <c r="J24" t="n">
-        <v>-0.3062</v>
+        <v>-1.3352</v>
       </c>
       <c r="K24" t="n">
-        <v>0.8587</v>
+        <v>-0.5828</v>
       </c>
       <c r="L24" t="n">
-        <v>-1.1649</v>
+        <v>-0.7524</v>
       </c>
       <c r="M24" t="n">
-        <v>-1.6647</v>
+        <v>-1.6731</v>
       </c>
       <c r="N24" t="n">
-        <v>-0.0176</v>
+        <v>-0.4314</v>
       </c>
       <c r="O24" t="n">
-        <v>-1.6471</v>
+        <v>-1.2417</v>
       </c>
       <c r="P24" t="n">
-        <v>-2.2683</v>
+        <v>0.2276</v>
       </c>
       <c r="Q24" t="n">
-        <v>-3.6293</v>
+        <v>-0.2276</v>
       </c>
       <c r="R24" t="n">
-        <v>1.361</v>
+        <v>0.4553</v>
       </c>
       <c r="S24" t="n">
-        <v>-1.7409</v>
+        <v>0.09420000000000001</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.0998</v>
+        <v>-0.3022</v>
       </c>
       <c r="U24" t="n">
-        <v>-1.6411</v>
+        <v>0.3964</v>
       </c>
       <c r="V24" t="n">
-        <v>0.1607</v>
+        <v>-2.7237</v>
       </c>
       <c r="W24" t="n">
-        <v>0.1607</v>
+        <v>1.0895</v>
       </c>
       <c r="X24" t="n">
-        <v>0</v>
+        <v>-3.8132</v>
       </c>
     </row>
     <row r="25">
@@ -2359,67 +2359,67 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-13.9504</v>
+        <v>-13.2441</v>
       </c>
       <c r="E25" t="n">
-        <v>-10.8381</v>
+        <v>-10.6682</v>
       </c>
       <c r="F25" t="n">
-        <v>-3.1123</v>
+        <v>-2.5759</v>
       </c>
       <c r="G25" t="n">
-        <v>-4.5221</v>
+        <v>-4.5301</v>
       </c>
       <c r="H25" t="n">
-        <v>-0.0866</v>
+        <v>-0.0862</v>
       </c>
       <c r="I25" t="n">
-        <v>-4.4355</v>
+        <v>-4.4439</v>
       </c>
       <c r="J25" t="n">
-        <v>-2.8787</v>
+        <v>-2.9122</v>
       </c>
       <c r="K25" t="n">
-        <v>0.4187</v>
+        <v>0.403</v>
       </c>
       <c r="L25" t="n">
-        <v>-3.2974</v>
+        <v>-3.3152</v>
       </c>
       <c r="M25" t="n">
-        <v>-1.6434</v>
+        <v>-1.6179</v>
       </c>
       <c r="N25" t="n">
-        <v>-0.5053</v>
+        <v>-0.4891</v>
       </c>
       <c r="O25" t="n">
-        <v>-1.1381</v>
+        <v>-1.1287</v>
       </c>
       <c r="P25" t="n">
-        <v>-6.5781</v>
+        <v>-6.6013</v>
       </c>
       <c r="Q25" t="n">
-        <v>-8.166</v>
+        <v>-8.194699999999999</v>
       </c>
       <c r="R25" t="n">
-        <v>1.5878</v>
+        <v>1.5934</v>
       </c>
       <c r="S25" t="n">
-        <v>-1.7575</v>
+        <v>-1.0232</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.8861</v>
+        <v>-0.6506999999999999</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.8713</v>
+        <v>-0.3725</v>
       </c>
       <c r="V25" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
       <c r="W25" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="X25" t="n">
-        <v>-2.1853</v>
+        <v>-2.1789</v>
       </c>
     </row>
     <row r="26">
@@ -2437,67 +2437,67 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-41.9471</v>
+        <v>-39.5785</v>
       </c>
       <c r="E26" t="n">
-        <v>-17.597</v>
+        <v>-17.916</v>
       </c>
       <c r="F26" t="n">
-        <v>-24.3501</v>
+        <v>-21.6624</v>
       </c>
       <c r="G26" t="n">
-        <v>-11.7949</v>
+        <v>-11.722</v>
       </c>
       <c r="H26" t="n">
-        <v>4.7976</v>
+        <v>4.81</v>
       </c>
       <c r="I26" t="n">
-        <v>-16.5925</v>
+        <v>-16.532</v>
       </c>
       <c r="J26" t="n">
-        <v>3.079800000000001</v>
+        <v>2.863</v>
       </c>
       <c r="K26" t="n">
-        <v>9.771000000000001</v>
+        <v>9.629299999999999</v>
       </c>
       <c r="L26" t="n">
-        <v>-6.6912</v>
+        <v>-6.7662</v>
       </c>
       <c r="M26" t="n">
-        <v>-14.8749</v>
+        <v>-14.5849</v>
       </c>
       <c r="N26" t="n">
-        <v>-4.9735</v>
+        <v>-4.819199999999999</v>
       </c>
       <c r="O26" t="n">
-        <v>-9.901400000000001</v>
+        <v>-9.765700000000001</v>
       </c>
       <c r="P26" t="n">
-        <v>-13.6099</v>
+        <v>-13.6579</v>
       </c>
       <c r="Q26" t="n">
-        <v>-23.8175</v>
+        <v>-23.9013</v>
       </c>
       <c r="R26" t="n">
-        <v>10.2075</v>
+        <v>10.2435</v>
       </c>
       <c r="S26" t="n">
-        <v>-10.9182</v>
+        <v>-8.593500000000002</v>
       </c>
       <c r="T26" t="n">
-        <v>-3.1906</v>
+        <v>-3.1853</v>
       </c>
       <c r="U26" t="n">
-        <v>-7.7276</v>
+        <v>-5.408099999999999</v>
       </c>
       <c r="V26" t="n">
-        <v>-5.624199999999999</v>
+        <v>-5.6052</v>
       </c>
       <c r="W26" t="n">
-        <v>6.3311</v>
+        <v>6.307600000000001</v>
       </c>
       <c r="X26" t="n">
-        <v>-11.9551</v>
+        <v>-11.9127</v>
       </c>
     </row>
   </sheetData>

--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104547_W10.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104547_W10.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X26"/>
+  <dimension ref="A1:Y26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -549,6 +549,11 @@
           <t>Def_FT</t>
         </is>
       </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Game_File</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -627,6 +632,11 @@
       <c r="X2" t="n">
         <v>0</v>
       </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>play_by_play_104547_W10.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -705,6 +715,11 @@
       <c r="X3" t="n">
         <v>0</v>
       </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>play_by_play_104547_W10.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -783,6 +798,11 @@
       <c r="X4" t="n">
         <v>0</v>
       </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>play_by_play_104547_W10.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -861,6 +881,11 @@
       <c r="X5" t="n">
         <v>0</v>
       </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>play_by_play_104547_W10.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -939,6 +964,11 @@
       <c r="X6" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>play_by_play_104547_W10.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1017,6 +1047,11 @@
       <c r="X7" t="n">
         <v>0</v>
       </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>play_by_play_104547_W10.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1095,6 +1130,11 @@
       <c r="X8" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>play_by_play_104547_W10.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1173,6 +1213,11 @@
       <c r="X9" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>play_by_play_104547_W10.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1251,6 +1296,11 @@
       <c r="X10" t="n">
         <v>-0.5447</v>
       </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>play_by_play_104547_W10.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1329,6 +1379,11 @@
       <c r="X11" t="n">
         <v>-1.2472</v>
       </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>play_by_play_104547_W10.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1407,6 +1462,11 @@
       <c r="X12" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>play_by_play_104547_W10.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1485,6 +1545,11 @@
       <c r="X13" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>play_by_play_104547_W10.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1563,6 +1628,7 @@
       <c r="X14" t="n">
         <v>-6.3077</v>
       </c>
+      <c r="Y14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1641,6 +1707,11 @@
       <c r="X15" t="n">
         <v>0</v>
       </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>play_by_play_104547_W10.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1719,6 +1790,11 @@
       <c r="X16" t="n">
         <v>0</v>
       </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>play_by_play_104547_W10.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1797,6 +1873,11 @@
       <c r="X17" t="n">
         <v>0</v>
       </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>play_by_play_104547_W10.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1875,6 +1956,11 @@
       <c r="X18" t="n">
         <v>0</v>
       </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>play_by_play_104547_W10.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1953,6 +2039,11 @@
       <c r="X19" t="n">
         <v>-1.2472</v>
       </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>play_by_play_104547_W10.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2031,6 +2122,11 @@
       <c r="X20" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>play_by_play_104547_W10.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2109,6 +2205,11 @@
       <c r="X21" t="n">
         <v>-2.8814</v>
       </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>play_by_play_104547_W10.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2187,6 +2288,11 @@
       <c r="X22" t="n">
         <v>-1.6342</v>
       </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>play_by_play_104547_W10.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2265,6 +2371,11 @@
       <c r="X23" t="n">
         <v>0</v>
       </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>play_by_play_104547_W10.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2343,6 +2454,11 @@
       <c r="X24" t="n">
         <v>-3.8132</v>
       </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>play_by_play_104547_W10.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2421,6 +2537,11 @@
       <c r="X25" t="n">
         <v>-2.1789</v>
       </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>play_by_play_104547_W10.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -2499,6 +2620,7 @@
       <c r="X26" t="n">
         <v>-11.9127</v>
       </c>
+      <c r="Y26" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
